--- a/AO.xlsx
+++ b/AO.xlsx
@@ -920,6 +920,7 @@
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>business_date</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>incrued_cost</t>
+  </si>
+  <si>
+    <t>Penalty</t>
   </si>
   <si>
     <t>Xajituu Gaddisaa</t>
@@ -910,20 +913,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,8 +953,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46216</v>
       </c>
@@ -960,19 +965,19 @@
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="F2">
         <v>2000</v>
       </c>
       <c r="G2">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -980,8 +985,11 @@
       <c r="I2">
         <v>-7000</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46216</v>
       </c>
@@ -989,19 +997,19 @@
         <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>928276274</v>
       </c>
       <c r="E3">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="F3">
         <v>2000</v>
       </c>
       <c r="G3">
-        <v>8700</v>
+        <v>8500</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1009,8 +1017,11 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46216</v>
       </c>
@@ -1018,7 +1029,7 @@
         <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>930308503</v>
@@ -1038,8 +1049,11 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46216</v>
       </c>
@@ -1047,10 +1061,10 @@
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>800</v>
@@ -1067,8 +1081,11 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46216</v>
       </c>
@@ -1076,7 +1093,7 @@
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>977677737</v>
@@ -1096,8 +1113,11 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46216</v>
       </c>
@@ -1105,7 +1125,7 @@
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>912672957</v>
@@ -1125,8 +1145,11 @@
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46216</v>
       </c>
@@ -1134,7 +1157,7 @@
         <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>913354650</v>
@@ -1154,8 +1177,11 @@
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46216</v>
       </c>
@@ -1163,7 +1189,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>920116666</v>
@@ -1183,8 +1209,11 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46216</v>
       </c>
@@ -1192,19 +1221,19 @@
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>912609998</v>
       </c>
       <c r="E10">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="H10">
         <v>10000</v>
@@ -1212,8 +1241,11 @@
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46219</v>
       </c>
@@ -1221,7 +1253,7 @@
         <v>1001</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>912861288</v>
@@ -1241,8 +1273,11 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46216</v>
       </c>
@@ -1250,7 +1285,7 @@
         <v>1010</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>912695064</v>
@@ -1270,8 +1305,11 @@
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46216</v>
       </c>
@@ -1279,7 +1317,7 @@
         <v>1011</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>922956646</v>
@@ -1299,8 +1337,11 @@
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46216</v>
       </c>
@@ -1308,7 +1349,7 @@
         <v>1012</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>919408998</v>
@@ -1328,8 +1369,11 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46216</v>
       </c>
@@ -1337,7 +1381,7 @@
         <v>1013</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>912861288</v>
@@ -1357,8 +1401,11 @@
       <c r="I15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46216</v>
       </c>
@@ -1366,7 +1413,7 @@
         <v>1014</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16">
         <v>910126329</v>
@@ -1386,8 +1433,11 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46216</v>
       </c>
@@ -1395,7 +1445,7 @@
         <v>1015</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>917307048</v>
@@ -1415,8 +1465,11 @@
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46216</v>
       </c>
@@ -1424,10 +1477,10 @@
         <v>1016</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <v>700</v>
@@ -1444,8 +1497,11 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46216</v>
       </c>
@@ -1453,10 +1509,10 @@
         <v>1017</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19">
         <v>1000</v>
@@ -1471,6 +1527,9 @@
         <v>0</v>
       </c>
       <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>0</v>
       </c>
     </row>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\AOL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\AOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -919,10 +919,6 @@
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1259,13 +1255,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>65967.210000000006</v>
+        <v>66167.210000000006</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>65967.210000000006</v>
+        <v>66167.210000000006</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1323,13 +1319,13 @@
         <v>922956646</v>
       </c>
       <c r="E13">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F13">
         <v>2000</v>
       </c>
       <c r="G13">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H13">
         <v>10000</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -917,7 +917,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1255,13 +1254,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>66167.210000000006</v>
+        <v>66367.210000000006</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>66167.210000000006</v>
+        <v>66367.210000000006</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1383,13 +1382,13 @@
         <v>912861288</v>
       </c>
       <c r="E15">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F15">
         <v>2000</v>
       </c>
       <c r="G15">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H15">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -917,7 +917,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1094,16 +1099,16 @@
         <v>977677737</v>
       </c>
       <c r="E6">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F6">
         <v>2000</v>
       </c>
       <c r="G6">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H6">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -917,12 +917,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1259,13 +1254,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>66367.210000000006</v>
+        <v>76567.210000000006</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>66367.210000000006</v>
+        <v>76567.210000000006</v>
       </c>
       <c r="H11">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -966,13 +966,13 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F2">
         <v>2000</v>
       </c>
       <c r="G2">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -998,13 +998,13 @@
         <v>928276274</v>
       </c>
       <c r="E3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F3">
         <v>2000</v>
       </c>
       <c r="G3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>930308503</v>
       </c>
       <c r="E4">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1126,13 +1126,13 @@
         <v>912672957</v>
       </c>
       <c r="E7">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F7">
         <v>2000</v>
       </c>
       <c r="G7">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1158,13 +1158,13 @@
         <v>913354650</v>
       </c>
       <c r="E8">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F8">
         <v>2000</v>
       </c>
       <c r="G8">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1190,22 +1190,19 @@
         <v>920116666</v>
       </c>
       <c r="E9">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F9">
         <v>2000</v>
       </c>
       <c r="G9">
-        <v>8500</v>
-      </c>
-      <c r="H9">
-        <v>5000</v>
+        <v>8700</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1222,13 +1219,13 @@
         <v>912609998</v>
       </c>
       <c r="E10">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H10">
         <v>10000</v>
@@ -1254,13 +1251,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>76567.210000000006</v>
+        <v>67773.399999999994</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>76567.210000000006</v>
+        <v>67773.399999999994</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1286,13 +1283,13 @@
         <v>912695064</v>
       </c>
       <c r="E12">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F12">
         <v>2000</v>
       </c>
       <c r="G12">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H12">
         <v>1000</v>
@@ -1350,13 +1347,13 @@
         <v>919408998</v>
       </c>
       <c r="E14">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H14">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -1103,7 +1103,7 @@
         <v>8700</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1291,9 +1291,6 @@
       <c r="G12">
         <v>8700</v>
       </c>
-      <c r="H12">
-        <v>1000</v>
-      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1323,9 +1320,6 @@
       <c r="G13">
         <v>8700</v>
       </c>
-      <c r="H13">
-        <v>10000</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1388,7 +1382,7 @@
         <v>8700</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1452,7 +1446,7 @@
         <v>1300</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I17">
         <v>0</v>
